--- a/data/trans_bre/IP21-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 10,45</t>
+          <t>-3,99; 10,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 8,03</t>
+          <t>-3,04; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,82</t>
+          <t>-3,92; 4,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,25</t>
+          <t>-7,68; 2,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 99,41</t>
+          <t>-25,1; 104,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 172,57</t>
+          <t>-35,94; 169,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 208,64</t>
+          <t>-59,29; 180,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,49</t>
+          <t>-100,0; 170,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,56; -0,29</t>
+          <t>-4,5; -0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,83</t>
+          <t>-3,32; 2,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,59</t>
+          <t>0,09; 4,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,92</t>
+          <t>-1,08; 3,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,77; 5,58</t>
+          <t>-88,13; 9,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 86,9</t>
+          <t>-52,12; 73,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 895,0</t>
+          <t>-14,01; 851,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 538,8</t>
+          <t>-57,28; 546,99</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,17</t>
+          <t>-4,95; 1,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,54</t>
+          <t>-4,69; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,97</t>
+          <t>-3,26; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,86</t>
+          <t>-2,32; 1,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,64</t>
+          <t>-100,0; 116,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 172,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,57; 194,53</t>
+          <t>-78,87; 151,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,29</t>
+          <t>-2,34; 1,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,45</t>
+          <t>-4,57; 0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,99</t>
+          <t>-4,8; 0,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,3</t>
+          <t>-2,89; 0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 577,4</t>
+          <t>-100,0; 605,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,59</t>
+          <t>-100,0; 63,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,55; 75,49</t>
+          <t>-86,71; 80,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,96</t>
+          <t>-2,5; 0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,27</t>
+          <t>-2,0; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,72</t>
+          <t>-1,26; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,8</t>
+          <t>-1,39; 0,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 26,77</t>
+          <t>-46,74; 22,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 34,49</t>
+          <t>-39,27; 35,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 81,72</t>
+          <t>-36,15; 77,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 80,43</t>
+          <t>-61,65; 76,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 10,68</t>
+          <t>-4,71; 10,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,95</t>
+          <t>-2,96; 7,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,67</t>
+          <t>-3,39; 4,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,36</t>
+          <t>-7,17; 2,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 104,19</t>
+          <t>-27,82; 104,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 169,95</t>
+          <t>-31,68; 160,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 180,55</t>
+          <t>-55,16; 206,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,45</t>
+          <t>-100,0; 211,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,01</t>
+          <t>-4,5; 0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,5</t>
+          <t>-3,49; 2,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,57</t>
+          <t>0,18; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,9</t>
+          <t>-1,29; 3,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 9,96</t>
+          <t>-87,63; 9,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 73,79</t>
+          <t>-51,5; 84,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 851,68</t>
+          <t>-9,66; 1103,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 546,99</t>
+          <t>-55,32; 570,69</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,11</t>
+          <t>-4,96; 0,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,54</t>
+          <t>-4,3; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,95</t>
+          <t>-3,48; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,72</t>
+          <t>-2,16; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,32</t>
+          <t>-100,0; 127,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 172,71</t>
+          <t>-100,0; 110,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 151,91</t>
+          <t>-79,12; 152,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,26</t>
+          <t>-2,05; 1,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,37</t>
+          <t>-4,46; 0,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 0,95</t>
+          <t>-4,59; 1,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,26</t>
+          <t>-3,06; 0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 605,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,48</t>
+          <t>-92,78; 81,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 80,47</t>
+          <t>-83,73; 117,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,82</t>
+          <t>-2,65; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,27</t>
+          <t>-2,2; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,67</t>
+          <t>-1,07; 1,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,81</t>
+          <t>-1,36; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 22,96</t>
+          <t>-48,52; 24,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 35,48</t>
+          <t>-40,67; 34,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 77,76</t>
+          <t>-31,76; 88,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 76,95</t>
+          <t>-58,23; 94,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-53,56%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 10,63</t>
+          <t>-3,85; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 7,82</t>
+          <t>-2,64; 8,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 4,83</t>
+          <t>-3,65; 4,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,05</t>
+          <t>-8,44; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 104,44</t>
+          <t>-24,67; 99,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 160,19</t>
+          <t>-27,78; 172,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 206,19</t>
+          <t>-55,44; 208,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,04</t>
+          <t>-100,0; 227,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,01</t>
+          <t>-4,56; -0,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,99</t>
+          <t>-3,48; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,71</t>
+          <t>0,08; 4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,95</t>
+          <t>-0,83; 4,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 9,41</t>
+          <t>-86,77; 5,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,5; 84,82</t>
+          <t>-54,13; 86,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 1103,54</t>
+          <t>-18,67; 895,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 570,69</t>
+          <t>-56,32; 643,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-8,96%</t>
+          <t>-6,31%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,99</t>
+          <t>-5,25; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,44</t>
+          <t>-4,58; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,83</t>
+          <t>-3,43; 1,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,62</t>
+          <t>-2,07; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,22</t>
+          <t>-100,0; 115,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 152,3</t>
+          <t>-80,57; 194,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-63,04%</t>
+          <t>-63,72%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,28</t>
+          <t>-2,02; 1,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,55</t>
+          <t>-4,37; 0,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,26</t>
+          <t>-5,24; 0,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,22</t>
+          <t>-3,03; 0,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 577,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,78; 81,21</t>
+          <t>-100,0; 87,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 117,91</t>
+          <t>-89,55; 75,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,26%</t>
+          <t>-13,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,9</t>
+          <t>-2,4; 0,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,21</t>
+          <t>-2,1; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,73</t>
+          <t>-1,09; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,93</t>
+          <t>-1,28; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 24,44</t>
+          <t>-44,93; 26,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 34,56</t>
+          <t>-40,92; 34,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 88,49</t>
+          <t>-31,15; 81,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 94,66</t>
+          <t>-59,93; 85,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-53,56%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.145735607180841</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.452439016001732</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5216623879647788</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.649402218434308</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2332675095892464</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3336431486257301</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1116103700909446</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5356030859758922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 10,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,64; 8,03</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,65; 4,82</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,44; 1,86</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-24,67; 99,41</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-27,78; 172,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-55,44; 208,64</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 227,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.850418845478894</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.636385583132982</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.65444325471281</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.439394304788351</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2467075471508419</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2778299256146908</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5543686262302399</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.44574487178072</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.033167946041512</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.815281362033844</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.856983497376253</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.9941405976197315</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.725691023976793</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.086373079437689</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.270337833053058</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,14</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-58,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>163,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,56; -0,29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,48; 2,83</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 4,59</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,83; 4,53</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-86,77; 5,58</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-54,13; 86,9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-18,67; 895,0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-56,32; 643,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.13820120517423</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.3489041973262074</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.073868837736432</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.436681540282207</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5807825672659562</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06994983652090812</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.637263972669342</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.8961648975221698</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-53,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-65,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-23,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-6,31%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.55733449400349</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.483079008781449</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.08165934154043333</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.8327869833590726</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8676645371339717</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5413469997410443</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1867051721712152</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5632297374371801</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,25; 1,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,58; 0,54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 1,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 1,87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 115,64</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-80,57; 194,53</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.2878559167471666</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.825388496742085</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.589483578558165</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.525258418592887</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.0558402291060577</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8689924314413636</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>8.949990152878797</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>6.431412863690515</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-26,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-60,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-46,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-63,72%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.790439100774621</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.595952975740157</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.6448478639332875</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.07700418726299882</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5382825321803995</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.6510385050999766</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2304628211112967</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.06313192464615601</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 1,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,37; 0,45</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,24; 0,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,03; 0,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 577,4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 87,59</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-89,55; 75,49</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.245936203596025</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.58319081364003</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.426379948549776</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.066988928751562</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-0.8056975333000946</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.170351299385679</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5414842540740786</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.973453965773382</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.868712006964963</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.156364237473498</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>1.945305572769649</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3555975317424704</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.812106189673468</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.713655012463069</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8400909948052128</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2678483773600146</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6065262419961138</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.4697889950760651</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6371831303414043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.02060408452803</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.37158752353044</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.237954730550202</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.032329217802473</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8955320613371065</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.292280533957708</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4544783772053698</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9938934820752923</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.2727576558661794</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>5.774014688968154</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8759248707785358</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7548696645449621</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-18,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-8,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-13,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 0,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 1,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 1,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 0,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-44,93; 26,77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-40,92; 34,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,15; 81,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-59,93; 85,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.8561467197220396</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3951512116622042</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2402932192317277</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.2100742091025754</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1866276102706194</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.08919723896881013</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.08647577327940296</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1300063969634311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.398571950441772</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.101441857150952</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.087424158193255</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.2787855173234</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4492504916061691</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4091779343206032</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3115208350124237</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5993129646885894</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9585977557150264</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.271333278005857</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.716591906254494</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.8725977201778876</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2676552916366228</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3448907100413863</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.8171663722079819</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8508486477832351</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1105,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
